--- a/src/templates/EscalaCrec.xlsx
+++ b/src/templates/EscalaCrec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\amer.prgx.com\Citrix\UserHomeDir\opined01\Desktop\Automation-EscalaCrec\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3412EB95-AEDF-4169-A6DD-CC93944C5324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC25D7C6-8F1B-4854-9343-63C0CE2B72EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{F9F17A23-D086-447D-9561-3922E85FFBB6}"/>
   </bookViews>
@@ -306,7 +306,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -341,7 +341,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
@@ -360,6 +359,17 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -788,12 +798,12 @@
     <col min="7" max="7" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="23" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="4.140625" style="6"/>
   </cols>
   <sheetData>
@@ -804,62 +814,62 @@
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="L1" s="27"/>
       <c r="M1" s="3"/>
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5"/>
@@ -872,28 +882,28 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5"/>
+      <c r="L5" s="28"/>
       <c r="M5"/>
       <c r="N5"/>
       <c r="O5" s="7"/>
     </row>
     <row r="6" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
@@ -926,7 +936,7 @@
       <c r="K7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="29" t="s">
         <v>13</v>
       </c>
       <c r="M7" s="9" t="s">
@@ -967,13 +977,13 @@
         <f>((G8/J8)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="16"/>
+      <c r="L8" s="20"/>
       <c r="M8" s="15">
         <f>G8*L8</f>
         <v>0</v>
       </c>
       <c r="N8" s="15"/>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <f>M8-N8</f>
         <v>0</v>
       </c>
@@ -1010,13 +1020,13 @@
         <f t="shared" ref="K9:K19" si="2">((G9/J9)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="16"/>
+      <c r="L9" s="20"/>
       <c r="M9" s="15">
         <f t="shared" ref="M9:M19" si="3">G9*L9</f>
         <v>0</v>
       </c>
       <c r="N9" s="15"/>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <f t="shared" ref="O9:O19" si="4">M9-N9</f>
         <v>0</v>
       </c>
@@ -1053,13 +1063,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L10" s="16"/>
+      <c r="L10" s="20"/>
       <c r="M10" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N10" s="15"/>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1096,13 +1106,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="16"/>
+      <c r="L11" s="20"/>
       <c r="M11" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N11" s="15"/>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1139,13 +1149,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L12" s="16"/>
+      <c r="L12" s="20"/>
       <c r="M12" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N12" s="15"/>
-      <c r="O12" s="17">
+      <c r="O12" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1182,13 +1192,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L13" s="16"/>
+      <c r="L13" s="20"/>
       <c r="M13" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13" s="15"/>
-      <c r="O13" s="17">
+      <c r="O13" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1225,13 +1235,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L14" s="16"/>
+      <c r="L14" s="20"/>
       <c r="M14" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="15"/>
-      <c r="O14" s="17">
+      <c r="O14" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1268,13 +1278,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L15" s="16"/>
+      <c r="L15" s="20"/>
       <c r="M15" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15" s="15"/>
-      <c r="O15" s="17">
+      <c r="O15" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1311,13 +1321,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L16" s="16"/>
+      <c r="L16" s="20"/>
       <c r="M16" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16" s="15"/>
-      <c r="O16" s="17">
+      <c r="O16" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1354,13 +1364,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L17" s="16"/>
+      <c r="L17" s="20"/>
       <c r="M17" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17" s="15"/>
-      <c r="O17" s="17">
+      <c r="O17" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1397,13 +1407,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L18" s="16"/>
+      <c r="L18" s="20"/>
       <c r="M18" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N18" s="15"/>
-      <c r="O18" s="17">
+      <c r="O18" s="16">
         <f>M18-N18</f>
         <v>0</v>
       </c>
@@ -1440,13 +1450,13 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L19" s="16"/>
+      <c r="L19" s="20"/>
       <c r="M19" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N19" s="15"/>
-      <c r="O19" s="17">
+      <c r="O19" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1455,17 +1465,17 @@
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="19">
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="18">
         <f>SUM(O8:O19)</f>
         <v>0</v>
       </c>
@@ -1504,18 +1514,18 @@
         <f t="shared" ref="K21" si="7">((G21/J21)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="20">
         <v>0</v>
       </c>
       <c r="M21" s="15">
         <f>G21*L21</f>
         <v>0</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="19">
         <f>+SUM(N8:N19)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="16">
         <f>M21-N21</f>
         <v>0</v>
       </c>
@@ -1531,28 +1541,28 @@
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
-      <c r="L22"/>
+      <c r="L22" s="28"/>
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
     </row>
     <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
@@ -1585,7 +1595,7 @@
       <c r="K24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="29" t="s">
         <v>13</v>
       </c>
       <c r="M24" s="9" t="s">
@@ -1628,13 +1638,13 @@
         <f>((G25/J25)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L25" s="16"/>
+      <c r="L25" s="20"/>
       <c r="M25" s="15">
         <f>G25*L25</f>
         <v>0</v>
       </c>
       <c r="N25" s="15"/>
-      <c r="O25" s="17">
+      <c r="O25" s="16">
         <f>M25-N25</f>
         <v>0</v>
       </c>
@@ -1669,13 +1679,13 @@
         <f t="shared" ref="K26:K36" si="12">((G26/J26)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L26" s="16"/>
+      <c r="L26" s="20"/>
       <c r="M26" s="15">
         <f t="shared" ref="M26:M36" si="13">G26*L26</f>
         <v>0</v>
       </c>
       <c r="N26" s="15"/>
-      <c r="O26" s="17">
+      <c r="O26" s="16">
         <f t="shared" ref="O26:O36" si="14">M26-N26</f>
         <v>0</v>
       </c>
@@ -1710,13 +1720,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L27" s="16"/>
+      <c r="L27" s="20"/>
       <c r="M27" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N27" s="15"/>
-      <c r="O27" s="17">
+      <c r="O27" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1751,13 +1761,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L28" s="16"/>
+      <c r="L28" s="20"/>
       <c r="M28" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N28" s="15"/>
-      <c r="O28" s="17">
+      <c r="O28" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1792,13 +1802,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L29" s="16"/>
+      <c r="L29" s="20"/>
       <c r="M29" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N29" s="15"/>
-      <c r="O29" s="17">
+      <c r="O29" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1833,13 +1843,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L30" s="16"/>
+      <c r="L30" s="20"/>
       <c r="M30" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N30" s="15"/>
-      <c r="O30" s="17">
+      <c r="O30" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1874,13 +1884,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L31" s="16"/>
+      <c r="L31" s="20"/>
       <c r="M31" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N31" s="15"/>
-      <c r="O31" s="17">
+      <c r="O31" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1915,13 +1925,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L32" s="16"/>
+      <c r="L32" s="20"/>
       <c r="M32" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N32" s="15"/>
-      <c r="O32" s="17">
+      <c r="O32" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1956,13 +1966,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L33" s="16"/>
+      <c r="L33" s="20"/>
       <c r="M33" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N33" s="15"/>
-      <c r="O33" s="17">
+      <c r="O33" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -1997,13 +2007,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="16"/>
+      <c r="L34" s="20"/>
       <c r="M34" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N34" s="15"/>
-      <c r="O34" s="17">
+      <c r="O34" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -2038,13 +2048,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="16"/>
+      <c r="L35" s="20"/>
       <c r="M35" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N35" s="15"/>
-      <c r="O35" s="17">
+      <c r="O35" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -2079,13 +2089,13 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="16"/>
+      <c r="L36" s="20"/>
       <c r="M36" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N36" s="15"/>
-      <c r="O36" s="17">
+      <c r="O36" s="16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -2094,17 +2104,17 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="19">
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="18">
         <f>SUM(O25:O36)</f>
         <v>0</v>
       </c>
@@ -2147,18 +2157,18 @@
         <f t="shared" ref="K38" si="17">((G38/J38)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="20">
         <v>0</v>
       </c>
       <c r="M38" s="15">
         <f t="shared" ref="M38" si="18">G38*L38</f>
         <v>0</v>
       </c>
-      <c r="N38" s="20">
+      <c r="N38" s="19">
         <f>+SUM(N25:N36)</f>
         <v>0</v>
       </c>
-      <c r="O38" s="17">
+      <c r="O38" s="16">
         <f>M38-N38</f>
         <v>0</v>
       </c>
@@ -2174,28 +2184,28 @@
       <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
-      <c r="L39"/>
+      <c r="L39" s="28"/>
       <c r="M39"/>
       <c r="N39"/>
       <c r="O39" s="7"/>
     </row>
     <row r="40" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
     </row>
     <row r="41" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
@@ -2228,7 +2238,7 @@
       <c r="K41" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="L41" s="29" t="s">
         <v>13</v>
       </c>
       <c r="M41" s="9" t="s">
@@ -2269,13 +2279,13 @@
         <f>((G42/J42)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L42" s="16"/>
+      <c r="L42" s="20"/>
       <c r="M42" s="15">
         <f>G42*L42</f>
         <v>0</v>
       </c>
       <c r="N42" s="15"/>
-      <c r="O42" s="17">
+      <c r="O42" s="16">
         <f>M42-N42</f>
         <v>0</v>
       </c>
@@ -2308,13 +2318,13 @@
         <f t="shared" ref="K43:K53" si="23">((G43/J43)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L43" s="16"/>
+      <c r="L43" s="20"/>
       <c r="M43" s="15">
         <f t="shared" ref="M43:M53" si="24">G43*L43</f>
         <v>0</v>
       </c>
       <c r="N43" s="15"/>
-      <c r="O43" s="17">
+      <c r="O43" s="16">
         <f t="shared" ref="O43:O53" si="25">M43-N43</f>
         <v>0</v>
       </c>
@@ -2347,13 +2357,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L44" s="16"/>
+      <c r="L44" s="20"/>
       <c r="M44" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N44" s="15"/>
-      <c r="O44" s="17">
+      <c r="O44" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2386,13 +2396,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L45" s="16"/>
+      <c r="L45" s="20"/>
       <c r="M45" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N45" s="15"/>
-      <c r="O45" s="17">
+      <c r="O45" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2425,13 +2435,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L46" s="16"/>
+      <c r="L46" s="20"/>
       <c r="M46" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N46" s="15"/>
-      <c r="O46" s="17">
+      <c r="O46" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2464,13 +2474,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L47" s="16"/>
+      <c r="L47" s="20"/>
       <c r="M47" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N47" s="15"/>
-      <c r="O47" s="17">
+      <c r="O47" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2503,13 +2513,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L48" s="16"/>
+      <c r="L48" s="20"/>
       <c r="M48" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N48" s="15"/>
-      <c r="O48" s="17">
+      <c r="O48" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2542,13 +2552,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L49" s="16"/>
+      <c r="L49" s="20"/>
       <c r="M49" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N49" s="15"/>
-      <c r="O49" s="17">
+      <c r="O49" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2581,13 +2591,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L50" s="16"/>
+      <c r="L50" s="20"/>
       <c r="M50" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N50" s="15"/>
-      <c r="O50" s="17">
+      <c r="O50" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2620,13 +2630,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L51" s="16"/>
+      <c r="L51" s="20"/>
       <c r="M51" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N51" s="15"/>
-      <c r="O51" s="17">
+      <c r="O51" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2659,13 +2669,13 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L52" s="16"/>
+      <c r="L52" s="20"/>
       <c r="M52" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N52" s="15"/>
-      <c r="O52" s="17">
+      <c r="O52" s="16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2683,28 +2693,28 @@
         <v>0</v>
       </c>
       <c r="E53" s="15"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="18">
+      <c r="F53" s="19"/>
+      <c r="G53" s="17">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
-      <c r="J53" s="18">
+      <c r="J53" s="17">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K53" s="18" t="e">
+      <c r="K53" s="17" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L53" s="16"/>
+      <c r="L53" s="20"/>
       <c r="M53" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N53" s="15"/>
-      <c r="O53" s="22">
+      <c r="O53" s="21">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -2713,17 +2723,17 @@
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="19">
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="18">
         <f>SUM(O42:O53)</f>
         <v>0</v>
       </c>
@@ -2766,43 +2776,43 @@
         <f>((G55/J55)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="21">
+      <c r="L55" s="20">
         <v>0</v>
       </c>
       <c r="M55" s="15">
         <f t="shared" ref="M55" si="29">G55*L55</f>
         <v>0</v>
       </c>
-      <c r="N55" s="20">
+      <c r="N55" s="19">
         <f>+SUM(N42:N53)</f>
         <v>0</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="16">
         <f>M55-N55</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N56" s="23"/>
-      <c r="O56" s="23"/>
+      <c r="N56" s="22"/>
+      <c r="O56" s="22"/>
     </row>
     <row r="57" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="25"/>
-      <c r="K57" s="25"/>
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
-      <c r="N57" s="25"/>
-      <c r="O57" s="25"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="24"/>
+      <c r="N57" s="24"/>
+      <c r="O57" s="24"/>
     </row>
     <row r="58" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="8" t="s">
@@ -2835,7 +2845,7 @@
       <c r="K58" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L58" s="10" t="s">
+      <c r="L58" s="29" t="s">
         <v>13</v>
       </c>
       <c r="M58" s="9" t="s">
@@ -2876,13 +2886,13 @@
         <f>((G59/J59)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L59" s="16"/>
+      <c r="L59" s="20"/>
       <c r="M59" s="15">
         <f>G59*L59</f>
         <v>0</v>
       </c>
       <c r="N59" s="15"/>
-      <c r="O59" s="17">
+      <c r="O59" s="16">
         <f>M59-N59</f>
         <v>0</v>
       </c>
@@ -2915,13 +2925,13 @@
         <f t="shared" ref="K60:K70" si="34">((G60/J60)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L60" s="16"/>
+      <c r="L60" s="20"/>
       <c r="M60" s="15">
         <f t="shared" ref="M60:M70" si="35">G60*L60</f>
         <v>0</v>
       </c>
       <c r="N60" s="15"/>
-      <c r="O60" s="17">
+      <c r="O60" s="16">
         <f t="shared" ref="O60:O70" si="36">M60-N60</f>
         <v>0</v>
       </c>
@@ -2954,13 +2964,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L61" s="16"/>
+      <c r="L61" s="20"/>
       <c r="M61" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N61" s="15"/>
-      <c r="O61" s="17">
+      <c r="O61" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -2993,13 +3003,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L62" s="16"/>
+      <c r="L62" s="20"/>
       <c r="M62" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N62" s="15"/>
-      <c r="O62" s="17">
+      <c r="O62" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3032,13 +3042,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L63" s="21"/>
+      <c r="L63" s="20"/>
       <c r="M63" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N63" s="15"/>
-      <c r="O63" s="17">
+      <c r="O63" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3071,13 +3081,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L64" s="16"/>
+      <c r="L64" s="20"/>
       <c r="M64" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N64" s="15"/>
-      <c r="O64" s="17">
+      <c r="O64" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3110,13 +3120,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L65" s="16"/>
+      <c r="L65" s="20"/>
       <c r="M65" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N65" s="15"/>
-      <c r="O65" s="17">
+      <c r="O65" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3149,13 +3159,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L66" s="16"/>
+      <c r="L66" s="20"/>
       <c r="M66" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N66" s="15"/>
-      <c r="O66" s="17">
+      <c r="O66" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3188,13 +3198,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L67" s="16"/>
+      <c r="L67" s="20"/>
       <c r="M67" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N67" s="15"/>
-      <c r="O67" s="17">
+      <c r="O67" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3227,13 +3237,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L68" s="16"/>
+      <c r="L68" s="20"/>
       <c r="M68" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N68" s="15"/>
-      <c r="O68" s="17">
+      <c r="O68" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3266,13 +3276,13 @@
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L69" s="16"/>
+      <c r="L69" s="20"/>
       <c r="M69" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N69" s="15"/>
-      <c r="O69" s="17">
+      <c r="O69" s="16">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3291,27 +3301,27 @@
       </c>
       <c r="E70" s="15"/>
       <c r="F70" s="15"/>
-      <c r="G70" s="18">
+      <c r="G70" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H70" s="15"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="18">
+      <c r="I70" s="19"/>
+      <c r="J70" s="17">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="K70" s="18" t="e">
+      <c r="K70" s="17" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L70" s="16"/>
+      <c r="L70" s="20"/>
       <c r="M70" s="15">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N70" s="15"/>
-      <c r="O70" s="22">
+      <c r="O70" s="21">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
@@ -3320,17 +3330,17 @@
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="19">
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="18">
         <f>SUM(O59:O70)</f>
         <v>0</v>
       </c>
@@ -3373,42 +3383,42 @@
         <f t="shared" ref="K72" si="40">((G72/J72)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L72" s="21">
+      <c r="L72" s="20">
         <v>0</v>
       </c>
       <c r="M72" s="15">
         <f t="shared" ref="M72" si="41">G72*L72</f>
         <v>0</v>
       </c>
-      <c r="N72" s="20">
+      <c r="N72" s="19">
         <f>+SUM(N59:N70)</f>
         <v>0</v>
       </c>
-      <c r="O72" s="17">
+      <c r="O72" s="16">
         <f>M72-N72</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O73" s="23"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" s="25"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
-      <c r="N74" s="25"/>
-      <c r="O74" s="25"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
+      <c r="L74" s="24"/>
+      <c r="M74" s="24"/>
+      <c r="N74" s="24"/>
+      <c r="O74" s="24"/>
     </row>
     <row r="75" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="8" t="s">
@@ -3441,7 +3451,7 @@
       <c r="K75" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L75" s="10" t="s">
+      <c r="L75" s="29" t="s">
         <v>13</v>
       </c>
       <c r="M75" s="9" t="s">
@@ -3482,13 +3492,13 @@
         <f>((G76/J76)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L76" s="16"/>
+      <c r="L76" s="20"/>
       <c r="M76" s="15">
         <f>G76*L76</f>
         <v>0</v>
       </c>
       <c r="N76" s="15"/>
-      <c r="O76" s="17">
+      <c r="O76" s="16">
         <f>M76-N76</f>
         <v>0</v>
       </c>
@@ -3521,13 +3531,13 @@
         <f t="shared" ref="K77:K87" si="46">((G77/J77)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L77" s="16"/>
+      <c r="L77" s="20"/>
       <c r="M77" s="15">
         <f t="shared" ref="M77:M87" si="47">G77*L77</f>
         <v>0</v>
       </c>
       <c r="N77" s="15"/>
-      <c r="O77" s="17">
+      <c r="O77" s="16">
         <f t="shared" ref="O77:O87" si="48">M77-N77</f>
         <v>0</v>
       </c>
@@ -3560,13 +3570,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L78" s="16"/>
+      <c r="L78" s="20"/>
       <c r="M78" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N78" s="15"/>
-      <c r="O78" s="17">
+      <c r="O78" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3599,13 +3609,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L79" s="16"/>
+      <c r="L79" s="20"/>
       <c r="M79" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N79" s="15"/>
-      <c r="O79" s="17">
+      <c r="O79" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3638,13 +3648,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L80" s="16"/>
+      <c r="L80" s="20"/>
       <c r="M80" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N80" s="15"/>
-      <c r="O80" s="17">
+      <c r="O80" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3677,13 +3687,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L81" s="16"/>
+      <c r="L81" s="20"/>
       <c r="M81" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N81" s="15"/>
-      <c r="O81" s="17">
+      <c r="O81" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3716,13 +3726,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L82" s="21"/>
+      <c r="L82" s="20"/>
       <c r="M82" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N82" s="15"/>
-      <c r="O82" s="17">
+      <c r="O82" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3755,13 +3765,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L83" s="16"/>
+      <c r="L83" s="20"/>
       <c r="M83" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N83" s="15"/>
-      <c r="O83" s="17">
+      <c r="O83" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3794,13 +3804,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L84" s="16"/>
+      <c r="L84" s="20"/>
       <c r="M84" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N84" s="15"/>
-      <c r="O84" s="17">
+      <c r="O84" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3833,13 +3843,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L85" s="16"/>
+      <c r="L85" s="20"/>
       <c r="M85" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N85" s="15"/>
-      <c r="O85" s="17">
+      <c r="O85" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3872,13 +3882,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L86" s="16"/>
+      <c r="L86" s="20"/>
       <c r="M86" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N86" s="15"/>
-      <c r="O86" s="17">
+      <c r="O86" s="16">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3897,27 +3907,27 @@
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="15"/>
-      <c r="G87" s="18">
+      <c r="G87" s="17">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
-      <c r="J87" s="18">
+      <c r="J87" s="17">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="K87" s="18" t="e">
+      <c r="K87" s="17" t="e">
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L87" s="16"/>
+      <c r="L87" s="20"/>
       <c r="M87" s="15">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="N87" s="15"/>
-      <c r="O87" s="22">
+      <c r="O87" s="21">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -3926,17 +3936,17 @@
       <c r="B88" s="13"/>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
-      <c r="N88" s="18"/>
-      <c r="O88" s="19">
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+      <c r="L88" s="30"/>
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+      <c r="O88" s="18">
         <f>SUM(O76:O87)</f>
         <v>0</v>
       </c>
@@ -3979,29 +3989,29 @@
         <f t="shared" ref="K89" si="52">((G89/J89)*100)-100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L89" s="21">
+      <c r="L89" s="20">
         <v>0</v>
       </c>
       <c r="M89" s="15">
         <f t="shared" ref="M89" si="53">G89*L89</f>
         <v>0</v>
       </c>
-      <c r="N89" s="20">
+      <c r="N89" s="19">
         <f>+SUM(N76:N87)</f>
         <v>0</v>
       </c>
-      <c r="O89" s="17">
+      <c r="O89" s="16">
         <f>M89-N89</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N90" s="23"/>
-      <c r="O90" s="23"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
     </row>
     <row r="91" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N91" s="23"/>
-      <c r="O91" s="23">
+      <c r="N91" s="22"/>
+      <c r="O91" s="22">
         <f>+O21+O38+O55+O72+O89</f>
         <v>0</v>
       </c>
